--- a/data/trans_orig/IP16A11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>48253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>52383</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93392</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>67538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101274</t>
+          <t>102018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90076</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149111</t>
+          <t>148470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188728</t>
+          <t>190120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24044</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65842</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48224</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133730</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>143635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228331</t>
+          <t>227983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>275842</t>
+          <t>271967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6929</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12895</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11952</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7951</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14635</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>78,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33978</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43241</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>39635</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20462</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54942</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48253</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77896</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52383</t>
+          <t>63040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73934</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64671</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81542</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>82845</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67538</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102018</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>164607</t>
+          <t>128607</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148470</t>
+          <t>116067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190120</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15568</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9887</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21332</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14091</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9510</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19915</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>29096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39696</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28078</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22314</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33759</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>27551</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21727</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32132</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>66,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>52,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35727</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>47388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>61889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52852</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42683</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63754</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35717</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47794</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>112627</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101725</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>122796</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>122347</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106238</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143635</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134915</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246487</t>
+          <t>201064</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>271967</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
